--- a/data/stx_xlsx/WIHL.ST.xlsx
+++ b/data/stx_xlsx/WIHL.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="364">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -589,6 +589,9 @@
   </si>
   <si>
     <t>Investment properties</t>
+  </si>
+  <si>
+    <t>Equipment (Do not use)</t>
   </si>
   <si>
     <t>Equipment</t>
@@ -1239,7 +1242,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1320,6 +1323,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -9814,7 +9820,7 @@
       <c r="X35" s="15"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="27" t="s">
         <v>190</v>
       </c>
       <c r="B36" s="15"/>
@@ -9865,7 +9871,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="17">
@@ -9929,7 +9935,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="18">
@@ -9993,7 +9999,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -10035,7 +10041,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B40" s="16">
         <v>176.05</v>
@@ -10077,7 +10083,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B41" s="16">
         <v>616.72</v>
@@ -10223,7 +10229,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="16">
@@ -10287,7 +10293,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="17">
@@ -10347,7 +10353,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -10379,7 +10385,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -10411,7 +10417,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -10443,7 +10449,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -10475,7 +10481,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -10507,7 +10513,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="16">
@@ -10547,7 +10553,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B52" s="26">
         <v>71441.65</v>
@@ -10621,7 +10627,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B53" s="26">
         <v>72056.17</v>
@@ -10695,7 +10701,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="16">
@@ -10759,7 +10765,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="17">
@@ -10823,7 +10829,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="16">
@@ -10887,7 +10893,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="16">
@@ -10937,7 +10943,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="16">
@@ -11045,7 +11051,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="17">
@@ -11083,7 +11089,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="17">
@@ -11133,7 +11139,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -11169,10 +11175,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="B63" s="16">
-        <v>1820.62</v>
+        <v>214</v>
       </c>
       <c r="C63" s="15"/>
       <c r="D63" s="15"/>
@@ -11201,7 +11204,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -11217,18 +11220,6 @@
       <c r="M64" s="15"/>
       <c r="N64" s="15"/>
       <c r="O64" s="15"/>
-      <c r="P64" s="16">
-        <v>1560.91</v>
-      </c>
-      <c r="Q64" s="16">
-        <v>442.58</v>
-      </c>
-      <c r="R64" s="16">
-        <v>1220.02</v>
-      </c>
-      <c r="S64" s="16">
-        <v>302.76</v>
-      </c>
       <c r="T64" s="15"/>
       <c r="U64" s="15"/>
       <c r="V64" s="15"/>
@@ -11237,14 +11228,26 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
+        <v>216</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1820.62</v>
+      </c>
+      <c r="C65" s="16">
+        <v>865.66</v>
+      </c>
+      <c r="D65" s="16">
+        <v>5027.78</v>
+      </c>
+      <c r="E65" s="16">
+        <v>928.09</v>
+      </c>
+      <c r="F65" s="16">
+        <v>3487.92</v>
+      </c>
+      <c r="G65" s="16">
+        <v>3130.51</v>
+      </c>
       <c r="H65" s="16">
         <v>1003.3</v>
       </c>
@@ -11257,7 +11260,9 @@
       <c r="K65" s="16">
         <v>827.88</v>
       </c>
-      <c r="L65" s="15"/>
+      <c r="L65" s="16">
+        <v>795.39</v>
+      </c>
       <c r="M65" s="15">
         <v>0.0</v>
       </c>
@@ -11265,10 +11270,18 @@
         <v>623.91</v>
       </c>
       <c r="O65" s="15"/>
-      <c r="P65" s="15"/>
-      <c r="Q65" s="15"/>
-      <c r="R65" s="15"/>
-      <c r="S65" s="15"/>
+      <c r="P65" s="16">
+        <v>1560.91</v>
+      </c>
+      <c r="Q65" s="16">
+        <v>442.58</v>
+      </c>
+      <c r="R65" s="16">
+        <v>1220.02</v>
+      </c>
+      <c r="S65" s="16">
+        <v>302.76</v>
+      </c>
       <c r="T65" s="15"/>
       <c r="U65" s="15"/>
       <c r="V65" s="15"/>
@@ -11277,7 +11290,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -11313,7 +11326,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -11347,24 +11360,9 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B68" s="15"/>
-      <c r="C68" s="16">
-        <v>865.66</v>
-      </c>
-      <c r="D68" s="16">
-        <v>5027.78</v>
-      </c>
-      <c r="E68" s="16">
-        <v>928.09</v>
-      </c>
-      <c r="F68" s="16">
-        <v>3487.92</v>
-      </c>
-      <c r="G68" s="16">
-        <v>3130.51</v>
-      </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
@@ -11385,7 +11383,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="17">
@@ -11425,7 +11423,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B70" s="20">
         <v>1820.62</v>
@@ -11495,7 +11493,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -11533,7 +11531,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -11579,7 +11577,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B73" s="16">
         <v>6862.6</v>
@@ -11649,7 +11647,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B74" s="15">
         <v>36357.77</v>
@@ -11703,7 +11701,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B75" s="16">
         <v>176.05</v>
@@ -11807,7 +11805,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B77" s="17">
         <v>87.48</v>
@@ -11863,7 +11861,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -11895,7 +11893,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="17">
@@ -11941,7 +11939,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="17">
@@ -11999,7 +11997,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="17">
@@ -12045,7 +12043,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="17">
@@ -12091,7 +12089,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="17">
@@ -12133,7 +12131,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B84" s="26">
         <v>43652.28</v>
@@ -12207,7 +12205,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B85" s="26">
         <v>45472.91</v>
@@ -12281,7 +12279,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="16">
@@ -12343,7 +12341,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="16">
@@ -12405,7 +12403,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B88" s="15"/>
       <c r="C88" s="16">
@@ -12467,7 +12465,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -12505,7 +12503,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15">
@@ -12567,7 +12565,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B91" s="26">
         <v>26583.27</v>
@@ -12683,7 +12681,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B93" s="26">
         <v>26583.27</v>
@@ -12757,7 +12755,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B94" s="26">
         <v>72056.17</v>
@@ -12831,7 +12829,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B95" s="16">
         <v>307.43</v>
@@ -12905,7 +12903,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B96" s="15">
         <v>0.0</v>
@@ -12979,7 +12977,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B97" s="16">
         <v>307.43</v>
@@ -13053,7 +13051,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B98" s="16">
         <v>108.65</v>
@@ -13107,7 +13105,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -13147,7 +13145,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -13177,7 +13175,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -13211,7 +13209,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
@@ -13241,7 +13239,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B103" s="15"/>
       <c r="C103" s="16">
@@ -13305,7 +13303,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B104" s="15"/>
       <c r="C104" s="15">
@@ -13359,7 +13357,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B105" s="15"/>
       <c r="C105" s="16">
@@ -13413,7 +13411,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B106" s="15"/>
       <c r="C106" s="16">
@@ -13467,7 +13465,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B107" s="15"/>
       <c r="C107" s="16">
@@ -13531,7 +13529,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B108" s="15"/>
       <c r="C108" s="16">
@@ -13595,7 +13593,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -13653,7 +13651,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B110" s="15"/>
       <c r="C110" s="17">
@@ -13691,7 +13689,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B111" s="15"/>
       <c r="C111" s="17">
@@ -13729,7 +13727,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B112" s="15"/>
       <c r="C112" s="16">
@@ -13767,7 +13765,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -13801,7 +13799,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -13831,7 +13829,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B115" s="16">
         <v>307.43</v>
@@ -13905,7 +13903,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B116" s="16">
         <v>307.43</v>
@@ -13979,7 +13977,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B117" s="15">
         <v>0.0</v>
@@ -14053,7 +14051,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="17">
         <v>1.0</v>
@@ -14127,7 +14125,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B119" s="16">
         <v>225.0</v>
@@ -14199,7 +14197,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -14231,7 +14229,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B121" s="15">
         <v>32000.0</v>
@@ -15194,7 +15192,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15593,73 +15591,73 @@
         <v>45</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15738,7 +15736,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15840,7 +15838,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -15878,7 +15876,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="16">
@@ -15930,7 +15928,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B22" s="16">
         <v>3290.82</v>
@@ -16068,7 +16066,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" s="17">
         <v>7.41</v>
@@ -16110,7 +16108,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" s="17">
         <v>23.3</v>
@@ -16176,7 +16174,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" s="22">
         <v>-1114.24</v>
@@ -16242,7 +16240,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" s="18">
         <v>-45.54</v>
@@ -16372,7 +16370,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -16422,7 +16420,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -16480,7 +16478,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B31" s="17">
         <v>10.59</v>
@@ -16546,7 +16544,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B32" s="16">
         <v>229.84</v>
@@ -16612,7 +16610,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -16644,7 +16642,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -16676,7 +16674,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B35" s="20">
         <v>2310.03</v>
@@ -16750,7 +16748,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="18">
@@ -16788,7 +16786,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -16836,7 +16834,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -16884,7 +16882,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -16916,7 +16914,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B40" s="22">
         <v>-2758.06</v>
@@ -16990,7 +16988,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" s="22">
         <v>-2899.99</v>
@@ -17042,7 +17040,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B42" s="16">
         <v>165.23</v>
@@ -17112,7 +17110,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B43" s="18">
         <v>-10.59</v>
@@ -17176,7 +17174,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -17218,7 +17216,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -17248,7 +17246,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B46" s="23">
         <v>-5503.41</v>
@@ -17322,7 +17320,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -17362,7 +17360,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B48" s="22">
         <v>-1042.22</v>
@@ -17430,7 +17428,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -17468,12 +17466,12 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B50" s="27">
+        <v>296</v>
+      </c>
+      <c r="B50" s="28">
         <v>-11497.21</v>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="28">
         <v>-12771.45</v>
       </c>
       <c r="D50" s="22">
@@ -17485,7 +17483,7 @@
       <c r="F50" s="22">
         <v>-4776.52</v>
       </c>
-      <c r="G50" s="27">
+      <c r="G50" s="28">
         <v>-11913.33</v>
       </c>
       <c r="H50" s="22">
@@ -17524,7 +17522,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B51" s="17">
         <v>12.71</v>
@@ -17570,7 +17568,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B52" s="15">
         <v>15562.28</v>
@@ -17634,7 +17632,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -17678,7 +17676,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -17710,7 +17708,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -17740,7 +17738,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -17772,7 +17770,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -17810,7 +17808,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -17844,7 +17842,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -17876,7 +17874,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -17906,7 +17904,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -17936,7 +17934,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B62" s="20">
         <v>3035.56</v>
@@ -18010,7 +18008,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B63" s="22">
         <v>-157.82</v>
@@ -18040,7 +18038,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B64" s="16">
         <v>450.51</v>
@@ -18110,7 +18108,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B65" s="15">
         <v>0.0</v>
@@ -18142,7 +18140,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B66" s="16">
         <v>287.58</v>
@@ -18212,7 +18210,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B67" s="23">
         <v>-157.82</v>
@@ -18286,7 +18284,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -19270,7 +19268,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19795,7 +19793,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19892,2347 +19890,2347 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B21" s="32">
         <v>63777.23</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>57096.63</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>47933.0</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>53278.18</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>52887.17</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>46918.37</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>37444.96</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>35583.96</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>28753.52</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>30698.33</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>24008.84</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <v>21286.98</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="32">
         <v>18275.36</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="32">
         <v>16737.55</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="32">
         <v>11562.01</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="32">
         <v>12092.44</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="32">
         <v>15690.58</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>11098.04</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>3057.07</v>
       </c>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="B22" s="32">
         <v>56546.2</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>52957.39</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>46059.13</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>44681.01</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>42799.45</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>34435.26</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>30960.82</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>28588.27</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>24397.77</v>
       </c>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31">
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32">
         <v>13539.75</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>10087.1</v>
       </c>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="B24" s="32">
         <v>33123.53</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>29170.99</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>22715.57</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>30760.65</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>29758.13</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>24862.67</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>15360.28</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>15096.73</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>12346.66</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>13754.46</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>10516.01</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>8348.02</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>6677.86</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>6501.81</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>4119.8</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>3417.15</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>3740.83</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>4994.81</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>3132.65</v>
       </c>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" s="32">
         <v>29896.52</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>28127.96</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>23806.49</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>22878.8</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>20646.11</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>15659.88</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>13263.99</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>12223.5</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>10202.39</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>9998.13</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>8073.94</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>6830.53</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>5345.58</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>4574.61</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>3650.3</v>
       </c>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="31" t="s">
+        <v>320</v>
+      </c>
+      <c r="B27" s="33">
         <v>107.74</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>94.89</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>73.89</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>100.06</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>96.8</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>80.87</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>49.96</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>49.11</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>40.16</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>44.74</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>34.21</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>27.15</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>21.72</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>21.15</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>13.4</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>11.12</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>12.17</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>16.25</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>10.19</v>
       </c>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>320</v>
-      </c>
-      <c r="B28" s="33">
+      <c r="A28" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="B28" s="34">
         <v>97.25</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="34">
         <v>91.49</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>77.44</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>74.42</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>67.16</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>50.94</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>43.15</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>39.76</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>33.19</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>32.52</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>26.26</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>22.22</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>17.39</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>14.88</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>11.87</v>
       </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" s="35">
         <v>-2.46</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>-0.25</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>-8.37</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>0.11</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>0.94</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <v>-10.84</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>-4.21</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>-16.85</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>-7.67</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>-16.56</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>-3.15</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>-20.17</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="35">
         <v>-13.84</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>-6.96</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>-7.48</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>-8.44</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>-2.68</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>-11.56</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="36">
         <v>0.0</v>
       </c>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="B31" s="34">
+      <c r="A31" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="B31" s="35">
         <v>-1.77</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>-3.34</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="35">
         <v>-4.15</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="35">
         <v>-4.92</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <v>-6.89</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>-11.08</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>-9.9</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>-12.85</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="35">
         <v>-11.88</v>
       </c>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="34">
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="35">
         <v>-7.51</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>-6.47</v>
       </c>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>324</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="B33" s="35">
+      <c r="A33" s="31" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" s="36">
         <v>2.1</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>2.3</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>2.68</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>1.79</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>1.7</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>1.52</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>2.14</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>2.05</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>2.17</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>1.94</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>2.08</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="36">
         <v>2.43</v>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="36">
         <v>2.59</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="36">
         <v>2.42</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>3.43</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>4.38</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>3.33</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="36">
         <v>1.72</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="36">
         <v>0.0</v>
       </c>
-      <c r="U33" s="35"/>
-      <c r="V33" s="35"/>
-      <c r="W33" s="35"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="36"/>
+      <c r="W33" s="36"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="B34" s="35">
+      <c r="A34" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" s="36">
         <v>2.09</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>1.98</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>1.93</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>1.79</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>1.84</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>1.9</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>2.08</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <v>2.11</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="36">
         <v>2.2</v>
       </c>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35">
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36">
         <v>2.91</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="36">
         <v>2.59</v>
       </c>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="35"/>
-      <c r="W34" s="35"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>327</v>
-      </c>
-      <c r="B35" s="35">
+      <c r="A35" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="B35" s="36">
         <v>3.01</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>3.29</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>3.82</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>2.56</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>2.43</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>2.17</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>3.05</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>2.93</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>3.1</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>2.78</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>2.98</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>3.47</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>3.69</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>3.46</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>4.91</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>6.25</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>4.75</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="36">
         <v>2.45</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="36">
         <v>0.0</v>
       </c>
-      <c r="U35" s="35"/>
-      <c r="V35" s="35"/>
-      <c r="W35" s="35"/>
+      <c r="U35" s="36"/>
+      <c r="V35" s="36"/>
+      <c r="W35" s="36"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="B36" s="35">
+      <c r="A36" s="31" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" s="36">
         <v>2.99</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>2.83</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>2.75</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>2.55</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>2.62</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>2.72</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>2.97</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>3.02</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>3.14</v>
       </c>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35">
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36">
         <v>4.15</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="36">
         <v>3.71</v>
       </c>
-      <c r="Q36" s="35"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="35"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>329</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>330</v>
-      </c>
-      <c r="B38" s="33">
+      <c r="A38" s="31" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" s="34">
         <v>1.39</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>1.29</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>1.03</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>1.44</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>1.47</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>1.48</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>1.01</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>1.11</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>1.14</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>1.48</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>1.57</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>1.28</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>1.27</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>1.44</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>1.12</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>0.9</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>1.0</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>1.55</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>1.3</v>
       </c>
-      <c r="U38" s="31"/>
-      <c r="V38" s="31"/>
-      <c r="W38" s="31"/>
+      <c r="U38" s="32"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="B39" s="33">
+      <c r="A39" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="B39" s="34">
         <v>1.32</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>1.33</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>1.29</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>1.33</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>1.27</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>1.24</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>1.2</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>1.28</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>1.33</v>
       </c>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="33">
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="34">
         <v>1.2</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>1.15</v>
       </c>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="B41" s="33">
+      <c r="A41" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" s="34">
         <v>1.39</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>1.29</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>1.03</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>1.44</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>1.47</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>1.48</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>1.01</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>1.11</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>1.14</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>1.48</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>1.57</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>1.28</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>1.27</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>1.44</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>1.12</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>0.9</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>1.0</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>1.55</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>1.3</v>
       </c>
-      <c r="U41" s="31"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="31"/>
+      <c r="U41" s="32"/>
+      <c r="V41" s="32"/>
+      <c r="W41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="B42" s="33">
+      <c r="A42" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="34">
         <v>1.32</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>1.33</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>1.29</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>1.33</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>1.27</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>1.24</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>1.2</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>1.28</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>1.33</v>
       </c>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="33">
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="34">
         <v>1.2</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>1.15</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="B44" s="33">
+      <c r="A44" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="B44" s="34">
         <v>7.72</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>7.47</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>7.24</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>10.32</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>9.27</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>8.89</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>5.86</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>6.42</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>6.42</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>6.73</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>5.76</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>5.19</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>5.18</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>5.76</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>3.89</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>3.18</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>4.28</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>6.03</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>4.97</v>
       </c>
-      <c r="U44" s="31"/>
-      <c r="V44" s="31"/>
-      <c r="W44" s="31"/>
+      <c r="U44" s="32"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="B45" s="33">
+      <c r="A45" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="B45" s="34">
         <v>8.3</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>8.55</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>8.35</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>8.3</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>7.53</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>6.96</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>6.22</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>6.14</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>5.91</v>
       </c>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="33">
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="34">
         <v>4.57</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>4.33</v>
       </c>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="31"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="32">
+      <c r="A47" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="33">
         <v>877.02</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="33">
         <v>106.33</v>
       </c>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="31"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>340</v>
-      </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
-      <c r="W48" s="29"/>
+      <c r="A48" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="30"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="B49" s="33">
+      <c r="A49" s="31" t="s">
+        <v>342</v>
+      </c>
+      <c r="B49" s="34">
         <v>18.8</v>
       </c>
-      <c r="C49" s="31"/>
-      <c r="D49" s="33">
+      <c r="C49" s="32"/>
+      <c r="D49" s="34">
         <v>10.47</v>
       </c>
-      <c r="E49" s="33">
+      <c r="E49" s="34">
         <v>9.41</v>
       </c>
-      <c r="F49" s="33">
+      <c r="F49" s="34">
         <v>12.74</v>
       </c>
-      <c r="G49" s="33">
+      <c r="G49" s="34">
         <v>9.03</v>
       </c>
-      <c r="H49" s="33">
+      <c r="H49" s="34">
         <v>6.54</v>
       </c>
-      <c r="I49" s="33">
+      <c r="I49" s="34">
         <v>5.87</v>
       </c>
-      <c r="J49" s="33">
+      <c r="J49" s="34">
         <v>4.37</v>
       </c>
-      <c r="K49" s="33">
+      <c r="K49" s="34">
         <v>5.77</v>
       </c>
-      <c r="L49" s="33">
+      <c r="L49" s="34">
         <v>27.72</v>
       </c>
-      <c r="M49" s="33">
+      <c r="M49" s="34">
         <v>8.33</v>
       </c>
-      <c r="N49" s="33">
+      <c r="N49" s="34">
         <v>9.48</v>
       </c>
-      <c r="O49" s="33">
+      <c r="O49" s="34">
         <v>6.19</v>
       </c>
-      <c r="P49" s="33">
+      <c r="P49" s="34">
         <v>9.82</v>
       </c>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="33">
+      <c r="Q49" s="32"/>
+      <c r="R49" s="34">
         <v>3.97</v>
       </c>
-      <c r="S49" s="33">
+      <c r="S49" s="34">
         <v>6.45</v>
       </c>
-      <c r="T49" s="33">
+      <c r="T49" s="34">
         <v>7.77</v>
       </c>
-      <c r="U49" s="31"/>
-      <c r="V49" s="31"/>
-      <c r="W49" s="31"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="B50" s="33">
+      <c r="A50" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="B50" s="34">
         <v>15.15</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>12.91</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>9.55</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <v>8.69</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <v>7.53</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <v>6.34</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <v>6.4</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <v>6.58</v>
       </c>
-      <c r="J50" s="33">
+      <c r="J50" s="34">
         <v>7.14</v>
       </c>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="33">
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="34">
         <v>7.22</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="34">
         <v>7.73</v>
       </c>
-      <c r="Q50" s="31"/>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="Q51" s="29"/>
-      <c r="R51" s="29"/>
-      <c r="S51" s="29"/>
-      <c r="T51" s="29"/>
-      <c r="U51" s="29"/>
-      <c r="V51" s="29"/>
-      <c r="W51" s="29"/>
+      <c r="A51" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="30"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="B52" s="33">
+      <c r="A52" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="B52" s="34">
         <v>18.89</v>
       </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="33">
+      <c r="C52" s="32"/>
+      <c r="D52" s="34">
         <v>10.55</v>
       </c>
-      <c r="E52" s="33">
+      <c r="E52" s="34">
         <v>9.43</v>
       </c>
-      <c r="F52" s="33">
+      <c r="F52" s="34">
         <v>12.82</v>
       </c>
-      <c r="G52" s="33">
+      <c r="G52" s="34">
         <v>9.07</v>
       </c>
-      <c r="H52" s="33">
+      <c r="H52" s="34">
         <v>6.55</v>
       </c>
-      <c r="I52" s="33">
+      <c r="I52" s="34">
         <v>5.88</v>
       </c>
-      <c r="J52" s="33">
+      <c r="J52" s="34">
         <v>4.38</v>
       </c>
-      <c r="K52" s="33">
+      <c r="K52" s="34">
         <v>5.77</v>
       </c>
-      <c r="L52" s="33">
+      <c r="L52" s="34">
         <v>27.79</v>
       </c>
-      <c r="M52" s="33">
+      <c r="M52" s="34">
         <v>8.34</v>
       </c>
-      <c r="N52" s="33">
+      <c r="N52" s="34">
         <v>9.48</v>
       </c>
-      <c r="O52" s="33">
+      <c r="O52" s="34">
         <v>8.09</v>
       </c>
-      <c r="P52" s="33">
+      <c r="P52" s="34">
         <v>9.88</v>
       </c>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="33">
+      <c r="Q52" s="32"/>
+      <c r="R52" s="34">
         <v>3.98</v>
       </c>
-      <c r="S52" s="33">
+      <c r="S52" s="34">
         <v>6.45</v>
       </c>
-      <c r="T52" s="33">
+      <c r="T52" s="34">
         <v>7.79</v>
       </c>
-      <c r="U52" s="31"/>
-      <c r="V52" s="31"/>
-      <c r="W52" s="31"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="B53" s="33">
+      <c r="A53" s="31" t="s">
+        <v>346</v>
+      </c>
+      <c r="B53" s="34">
         <v>15.24</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>12.99</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="34">
         <v>9.59</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <v>8.72</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <v>7.55</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <v>6.35</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>6.4</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <v>6.58</v>
       </c>
-      <c r="J53" s="33">
+      <c r="J53" s="34">
         <v>7.14</v>
       </c>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="33">
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="34">
         <v>7.85</v>
       </c>
-      <c r="P53" s="33">
+      <c r="P53" s="34">
         <v>7.76</v>
       </c>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>346</v>
-      </c>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
-      <c r="N54" s="29"/>
-      <c r="O54" s="29"/>
-      <c r="P54" s="29"/>
-      <c r="Q54" s="29"/>
-      <c r="R54" s="29"/>
-      <c r="S54" s="29"/>
-      <c r="T54" s="29"/>
-      <c r="U54" s="29"/>
-      <c r="V54" s="29"/>
-      <c r="W54" s="29"/>
+      <c r="A54" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="30"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="B55" s="33">
+      <c r="A55" s="31" t="s">
+        <v>348</v>
+      </c>
+      <c r="B55" s="34">
         <v>25.63</v>
       </c>
-      <c r="C55" s="33">
+      <c r="C55" s="34">
         <v>16.61</v>
       </c>
-      <c r="D55" s="33">
+      <c r="D55" s="34">
         <v>19.49</v>
       </c>
-      <c r="E55" s="33">
+      <c r="E55" s="34">
         <v>31.73</v>
       </c>
-      <c r="F55" s="33">
+      <c r="F55" s="34">
         <v>19.15</v>
       </c>
-      <c r="G55" s="33">
+      <c r="G55" s="34">
         <v>18.53</v>
       </c>
-      <c r="H55" s="33">
+      <c r="H55" s="34">
         <v>14.93</v>
       </c>
-      <c r="I55" s="33">
+      <c r="I55" s="34">
         <v>29.24</v>
       </c>
-      <c r="J55" s="33">
+      <c r="J55" s="34">
         <v>17.8</v>
       </c>
-      <c r="K55" s="33">
+      <c r="K55" s="34">
         <v>33.38</v>
       </c>
-      <c r="L55" s="33">
+      <c r="L55" s="34">
         <v>13.88</v>
       </c>
-      <c r="M55" s="33">
+      <c r="M55" s="34">
         <v>19.83</v>
       </c>
-      <c r="N55" s="33">
+      <c r="N55" s="34">
         <v>9.53</v>
       </c>
-      <c r="O55" s="33">
+      <c r="O55" s="34">
         <v>12.43</v>
       </c>
-      <c r="P55" s="33">
+      <c r="P55" s="34">
         <v>11.7</v>
       </c>
-      <c r="Q55" s="33">
+      <c r="Q55" s="34">
         <v>6.33</v>
       </c>
-      <c r="R55" s="33">
+      <c r="R55" s="34">
         <v>79.16</v>
       </c>
-      <c r="S55" s="33">
+      <c r="S55" s="34">
         <v>24.38</v>
       </c>
-      <c r="T55" s="33">
+      <c r="T55" s="34">
         <v>24.73</v>
       </c>
-      <c r="U55" s="31"/>
-      <c r="V55" s="31"/>
-      <c r="W55" s="31"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="B56" s="33">
+      <c r="A56" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="B56" s="34">
         <v>1.32</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <v>1.33</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="34">
         <v>1.29</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <v>1.33</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <v>1.27</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="34">
         <v>1.24</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>1.2</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>1.28</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="34">
         <v>1.33</v>
       </c>
-      <c r="K56" s="31"/>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-      <c r="N56" s="31"/>
-      <c r="O56" s="33">
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="34">
         <v>1.2</v>
       </c>
-      <c r="P56" s="33">
+      <c r="P56" s="34">
         <v>1.15</v>
       </c>
-      <c r="Q56" s="31"/>
-      <c r="R56" s="31"/>
-      <c r="S56" s="31"/>
-      <c r="T56" s="31"/>
-      <c r="U56" s="31"/>
-      <c r="V56" s="31"/>
-      <c r="W56" s="31"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
-      <c r="M57" s="29"/>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
-      <c r="Q57" s="29"/>
-      <c r="R57" s="29"/>
-      <c r="S57" s="29"/>
-      <c r="T57" s="29"/>
-      <c r="U57" s="29"/>
-      <c r="V57" s="29"/>
-      <c r="W57" s="29"/>
+      <c r="A57" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="30"/>
+      <c r="P57" s="30"/>
+      <c r="Q57" s="30"/>
+      <c r="R57" s="30"/>
+      <c r="S57" s="30"/>
+      <c r="T57" s="30"/>
+      <c r="U57" s="30"/>
+      <c r="V57" s="30"/>
+      <c r="W57" s="30"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>350</v>
-      </c>
-      <c r="B58" s="31">
+      <c r="A58" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="B58" s="32">
         <v>0.0</v>
       </c>
-      <c r="C58" s="31"/>
-      <c r="D58" s="36">
+      <c r="C58" s="32"/>
+      <c r="D58" s="37">
         <v>-0.33</v>
       </c>
-      <c r="E58" s="33">
+      <c r="E58" s="34">
         <v>0.19</v>
       </c>
-      <c r="F58" s="36">
+      <c r="F58" s="37">
         <v>-0.53</v>
       </c>
-      <c r="G58" s="33">
+      <c r="G58" s="34">
         <v>0.42</v>
       </c>
-      <c r="H58" s="36">
+      <c r="H58" s="37">
         <v>-1.02</v>
       </c>
-      <c r="I58" s="36">
+      <c r="I58" s="37">
         <v>-0.43</v>
       </c>
-      <c r="J58" s="33">
+      <c r="J58" s="34">
         <v>0.14</v>
       </c>
-      <c r="K58" s="33">
+      <c r="K58" s="34">
         <v>0.01</v>
       </c>
-      <c r="L58" s="36">
+      <c r="L58" s="37">
         <v>-0.44</v>
       </c>
-      <c r="M58" s="33">
+      <c r="M58" s="34">
         <v>0.29</v>
       </c>
-      <c r="N58" s="31"/>
-      <c r="O58" s="33">
+      <c r="N58" s="32"/>
+      <c r="O58" s="34">
         <v>0.1</v>
       </c>
-      <c r="P58" s="33">
+      <c r="P58" s="34">
         <v>0.01</v>
       </c>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="33">
+      <c r="Q58" s="32"/>
+      <c r="R58" s="34">
         <v>0.13</v>
       </c>
-      <c r="S58" s="33">
+      <c r="S58" s="34">
         <v>0.08</v>
       </c>
-      <c r="T58" s="33">
+      <c r="T58" s="34">
         <v>0.2</v>
       </c>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="31"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="B59" s="36">
+      <c r="A59" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" s="37">
         <v>-1.49</v>
       </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="36">
+      <c r="C59" s="32"/>
+      <c r="D59" s="37">
         <v>-4.21</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <v>3.64</v>
       </c>
-      <c r="F59" s="36">
+      <c r="F59" s="37">
         <v>-15.62</v>
       </c>
-      <c r="G59" s="33">
+      <c r="G59" s="34">
         <v>0.13</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>0.36</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>0.26</v>
       </c>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="33">
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="34">
         <v>0.55</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="34">
         <v>0.91</v>
       </c>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
-      <c r="W59" s="31"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="32"/>
+      <c r="T59" s="32"/>
+      <c r="U59" s="32"/>
+      <c r="V59" s="32"/>
+      <c r="W59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>352</v>
-      </c>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-      <c r="N60" s="29"/>
-      <c r="O60" s="29"/>
-      <c r="P60" s="29"/>
-      <c r="Q60" s="29"/>
-      <c r="R60" s="29"/>
-      <c r="S60" s="29"/>
-      <c r="T60" s="29"/>
-      <c r="U60" s="29"/>
-      <c r="V60" s="29"/>
-      <c r="W60" s="29"/>
+      <c r="A60" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+      <c r="S60" s="30"/>
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="30"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="B61" s="33">
+      <c r="A61" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="B61" s="34">
         <v>14.86</v>
       </c>
-      <c r="C61" s="33">
+      <c r="C61" s="34">
         <v>14.61</v>
       </c>
-      <c r="D61" s="33">
+      <c r="D61" s="34">
         <v>15.27</v>
       </c>
-      <c r="E61" s="33">
+      <c r="E61" s="34">
         <v>17.87</v>
       </c>
-      <c r="F61" s="33">
+      <c r="F61" s="34">
         <v>16.48</v>
       </c>
-      <c r="G61" s="33">
+      <c r="G61" s="34">
         <v>16.77</v>
       </c>
-      <c r="H61" s="33">
+      <c r="H61" s="34">
         <v>14.3</v>
       </c>
-      <c r="I61" s="33">
+      <c r="I61" s="34">
         <v>15.13</v>
       </c>
-      <c r="J61" s="33">
+      <c r="J61" s="34">
         <v>14.94</v>
       </c>
-      <c r="K61" s="33">
+      <c r="K61" s="34">
         <v>15.02</v>
       </c>
-      <c r="L61" s="33">
+      <c r="L61" s="34">
         <v>13.15</v>
       </c>
-      <c r="M61" s="33">
+      <c r="M61" s="34">
         <v>13.23</v>
       </c>
-      <c r="N61" s="33">
+      <c r="N61" s="34">
         <v>14.19</v>
       </c>
-      <c r="O61" s="33">
+      <c r="O61" s="34">
         <v>14.91</v>
       </c>
-      <c r="P61" s="33">
+      <c r="P61" s="34">
         <v>11.56</v>
       </c>
-      <c r="Q61" s="33">
+      <c r="Q61" s="34">
         <v>11.64</v>
       </c>
-      <c r="R61" s="33">
+      <c r="R61" s="34">
         <v>18.03</v>
       </c>
-      <c r="S61" s="33">
+      <c r="S61" s="34">
         <v>13.41</v>
       </c>
-      <c r="T61" s="33">
+      <c r="T61" s="34">
         <v>4.89</v>
       </c>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="31"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="B62" s="33">
+      <c r="A62" s="31" t="s">
+        <v>355</v>
+      </c>
+      <c r="B62" s="34">
         <v>15.69</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>16.1</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>16.16</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>16.2</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>15.62</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>15.3</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>14.52</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>14.36</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>14.14</v>
       </c>
-      <c r="K62" s="31"/>
-      <c r="L62" s="31"/>
-      <c r="M62" s="31"/>
-      <c r="N62" s="31"/>
-      <c r="O62" s="33">
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32"/>
+      <c r="N62" s="32"/>
+      <c r="O62" s="34">
         <v>13.83</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>12.26</v>
       </c>
-      <c r="Q62" s="31"/>
-      <c r="R62" s="31"/>
-      <c r="S62" s="31"/>
-      <c r="T62" s="31"/>
-      <c r="U62" s="31"/>
-      <c r="V62" s="31"/>
-      <c r="W62" s="31"/>
+      <c r="Q62" s="32"/>
+      <c r="R62" s="32"/>
+      <c r="S62" s="32"/>
+      <c r="T62" s="32"/>
+      <c r="U62" s="32"/>
+      <c r="V62" s="32"/>
+      <c r="W62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="29"/>
-      <c r="T63" s="29"/>
-      <c r="U63" s="29"/>
-      <c r="V63" s="29"/>
-      <c r="W63" s="29"/>
+      <c r="A63" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="30"/>
+      <c r="N63" s="30"/>
+      <c r="O63" s="30"/>
+      <c r="P63" s="30"/>
+      <c r="Q63" s="30"/>
+      <c r="R63" s="30"/>
+      <c r="S63" s="30"/>
+      <c r="T63" s="30"/>
+      <c r="U63" s="30"/>
+      <c r="V63" s="30"/>
+      <c r="W63" s="30"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="B64" s="33">
+      <c r="A64" s="31" t="s">
+        <v>357</v>
+      </c>
+      <c r="B64" s="34">
         <v>21.32</v>
       </c>
-      <c r="C64" s="33">
+      <c r="C64" s="34">
         <v>21.11</v>
       </c>
-      <c r="D64" s="33">
+      <c r="D64" s="34">
         <v>22.58</v>
       </c>
-      <c r="E64" s="33">
+      <c r="E64" s="34">
         <v>25.82</v>
       </c>
-      <c r="F64" s="33">
+      <c r="F64" s="34">
         <v>23.31</v>
       </c>
-      <c r="G64" s="33">
+      <c r="G64" s="34">
         <v>24.11</v>
       </c>
-      <c r="H64" s="33">
+      <c r="H64" s="34">
         <v>20.42</v>
       </c>
-      <c r="I64" s="33">
+      <c r="I64" s="34">
         <v>21.36</v>
       </c>
-      <c r="J64" s="33">
+      <c r="J64" s="34">
         <v>20.68</v>
       </c>
-      <c r="K64" s="33">
+      <c r="K64" s="34">
         <v>20.91</v>
       </c>
-      <c r="L64" s="33">
+      <c r="L64" s="34">
         <v>18.34</v>
       </c>
-      <c r="M64" s="33">
+      <c r="M64" s="34">
         <v>18.79</v>
       </c>
-      <c r="N64" s="33">
+      <c r="N64" s="34">
         <v>20.06</v>
       </c>
-      <c r="O64" s="33">
+      <c r="O64" s="34">
         <v>21.7</v>
       </c>
-      <c r="P64" s="33">
+      <c r="P64" s="34">
         <v>16.65</v>
       </c>
-      <c r="Q64" s="33">
+      <c r="Q64" s="34">
         <v>16.91</v>
       </c>
-      <c r="R64" s="33">
+      <c r="R64" s="34">
         <v>26.84</v>
       </c>
-      <c r="S64" s="33">
+      <c r="S64" s="34">
         <v>20.31</v>
       </c>
-      <c r="T64" s="33">
+      <c r="T64" s="34">
         <v>7.63</v>
       </c>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="B65" s="33">
+      <c r="A65" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B65" s="34">
         <v>22.65</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>23.26</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>23.3</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>23.14</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>22.14</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>21.63</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>20.39</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>20.11</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>19.79</v>
       </c>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="31"/>
-      <c r="O65" s="33">
+      <c r="K65" s="32"/>
+      <c r="L65" s="32"/>
+      <c r="M65" s="32"/>
+      <c r="N65" s="32"/>
+      <c r="O65" s="34">
         <v>20.29</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="34">
         <v>18.18</v>
       </c>
-      <c r="Q65" s="31"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="31"/>
-      <c r="T65" s="31"/>
-      <c r="U65" s="31"/>
-      <c r="V65" s="31"/>
-      <c r="W65" s="31"/>
+      <c r="Q65" s="32"/>
+      <c r="R65" s="32"/>
+      <c r="S65" s="32"/>
+      <c r="T65" s="32"/>
+      <c r="U65" s="32"/>
+      <c r="V65" s="32"/>
+      <c r="W65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>358</v>
-      </c>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
-      <c r="M66" s="29"/>
-      <c r="N66" s="29"/>
-      <c r="O66" s="29"/>
-      <c r="P66" s="29"/>
-      <c r="Q66" s="29"/>
-      <c r="R66" s="29"/>
-      <c r="S66" s="29"/>
-      <c r="T66" s="29"/>
-      <c r="U66" s="29"/>
-      <c r="V66" s="29"/>
-      <c r="W66" s="29"/>
+      <c r="A66" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="30"/>
+      <c r="O66" s="30"/>
+      <c r="P66" s="30"/>
+      <c r="Q66" s="30"/>
+      <c r="R66" s="30"/>
+      <c r="S66" s="30"/>
+      <c r="T66" s="30"/>
+      <c r="U66" s="30"/>
+      <c r="V66" s="30"/>
+      <c r="W66" s="30"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
-        <v>359</v>
-      </c>
-      <c r="B67" s="33">
+      <c r="A67" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="B67" s="34">
         <v>38.36</v>
       </c>
-      <c r="C67" s="33">
+      <c r="C67" s="34">
         <v>29.38</v>
       </c>
-      <c r="D67" s="33">
+      <c r="D67" s="34">
         <v>26.22</v>
       </c>
-      <c r="E67" s="33">
+      <c r="E67" s="34">
         <v>32.36</v>
       </c>
-      <c r="F67" s="33">
+      <c r="F67" s="34">
         <v>27.66</v>
       </c>
-      <c r="G67" s="33">
+      <c r="G67" s="34">
         <v>29.71</v>
       </c>
-      <c r="H67" s="33">
+      <c r="H67" s="34">
         <v>25.77</v>
       </c>
-      <c r="I67" s="33">
+      <c r="I67" s="34">
         <v>27.38</v>
       </c>
-      <c r="J67" s="33">
+      <c r="J67" s="34">
         <v>28.5</v>
       </c>
-      <c r="K67" s="33">
+      <c r="K67" s="34">
         <v>28.65</v>
       </c>
-      <c r="L67" s="33">
+      <c r="L67" s="34">
         <v>26.51</v>
       </c>
-      <c r="M67" s="33">
+      <c r="M67" s="34">
         <v>29.33</v>
       </c>
-      <c r="N67" s="33">
+      <c r="N67" s="34">
         <v>28.58</v>
       </c>
-      <c r="O67" s="33">
+      <c r="O67" s="34">
         <v>30.47</v>
       </c>
-      <c r="P67" s="33">
+      <c r="P67" s="34">
         <v>25.38</v>
       </c>
-      <c r="Q67" s="33">
+      <c r="Q67" s="34">
         <v>25.56</v>
       </c>
-      <c r="R67" s="33">
+      <c r="R67" s="34">
         <v>22.26</v>
       </c>
-      <c r="S67" s="33">
+      <c r="S67" s="34">
         <v>30.94</v>
       </c>
-      <c r="T67" s="33">
+      <c r="T67" s="34">
         <v>8.7</v>
       </c>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
-      <c r="W67" s="31"/>
+      <c r="U67" s="32"/>
+      <c r="V67" s="32"/>
+      <c r="W67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>360</v>
-      </c>
-      <c r="B68" s="33">
+      <c r="A68" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B68" s="34">
         <v>30.52</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <v>28.98</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <v>28.33</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>28.69</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>27.82</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>27.99</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>27.25</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="34">
         <v>28.0</v>
       </c>
-      <c r="J68" s="33">
+      <c r="J68" s="34">
         <v>28.27</v>
       </c>
-      <c r="K68" s="31"/>
-      <c r="L68" s="31"/>
-      <c r="M68" s="31"/>
-      <c r="N68" s="31"/>
-      <c r="O68" s="33">
+      <c r="K68" s="32"/>
+      <c r="L68" s="32"/>
+      <c r="M68" s="32"/>
+      <c r="N68" s="32"/>
+      <c r="O68" s="34">
         <v>26.36</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="34">
         <v>22.74</v>
       </c>
-      <c r="Q68" s="31"/>
-      <c r="R68" s="31"/>
-      <c r="S68" s="31"/>
-      <c r="T68" s="31"/>
-      <c r="U68" s="31"/>
-      <c r="V68" s="31"/>
-      <c r="W68" s="31"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="32"/>
+      <c r="T68" s="32"/>
+      <c r="U68" s="32"/>
+      <c r="V68" s="32"/>
+      <c r="W68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="29"/>
-      <c r="P69" s="29"/>
-      <c r="Q69" s="29"/>
-      <c r="R69" s="29"/>
-      <c r="S69" s="29"/>
-      <c r="T69" s="29"/>
-      <c r="U69" s="29"/>
-      <c r="V69" s="29"/>
-      <c r="W69" s="29"/>
+      <c r="A69" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
+      <c r="N69" s="30"/>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="30"/>
+      <c r="R69" s="30"/>
+      <c r="S69" s="30"/>
+      <c r="T69" s="30"/>
+      <c r="U69" s="30"/>
+      <c r="V69" s="30"/>
+      <c r="W69" s="30"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="32">
+      <c r="A70" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="33">
         <v>1519.02</v>
       </c>
-      <c r="F70" s="32">
+      <c r="F70" s="33">
         <v>188.99</v>
       </c>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-      <c r="N70" s="31"/>
-      <c r="O70" s="31"/>
-      <c r="P70" s="31"/>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
-      <c r="S70" s="31"/>
-      <c r="T70" s="31"/>
-      <c r="U70" s="31"/>
-      <c r="V70" s="31"/>
-      <c r="W70" s="31"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="32"/>
+      <c r="T70" s="32"/>
+      <c r="U70" s="32"/>
+      <c r="V70" s="32"/>
+      <c r="W70" s="32"/>
     </row>
     <row r="71" ht="15.75" customHeight="1"/>
     <row r="72" ht="15.75" customHeight="1"/>

--- a/data/stx_xlsx/WIHL.ST.xlsx
+++ b/data/stx_xlsx/WIHL.ST.xlsx
@@ -9816,8 +9816,12 @@
       <c r="V35" s="16">
         <v>6629.33</v>
       </c>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
+      <c r="W35" s="16">
+        <v>6308.76</v>
+      </c>
+      <c r="X35" s="16">
+        <v>5321.57</v>
+      </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="27" t="s">
@@ -9866,8 +9870,12 @@
       <c r="T36" s="15"/>
       <c r="U36" s="15"/>
       <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
+      <c r="W36" s="17">
+        <v>6.49</v>
+      </c>
+      <c r="X36" s="17">
+        <v>5.59</v>
+      </c>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">

--- a/data/stx_xlsx/WIHL.ST.xlsx
+++ b/data/stx_xlsx/WIHL.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="365">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -766,6 +766,9 @@
   </si>
   <si>
     <t>Investment propert PPE G</t>
+  </si>
+  <si>
+    <t>Current interest-bearing liabilities (Do not use)</t>
   </si>
   <si>
     <t>Debt Maturing Within 2 Years</t>
@@ -13246,8 +13249,8 @@
       <c r="X102" s="15"/>
     </row>
     <row r="103" ht="15.0" customHeight="1">
-      <c r="A103" s="14" t="s">
-        <v>216</v>
+      <c r="A103" s="27" t="s">
+        <v>249</v>
       </c>
       <c r="B103" s="15"/>
       <c r="C103" s="16">
@@ -13311,7 +13314,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B104" s="15"/>
       <c r="C104" s="15">
@@ -13365,7 +13368,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B105" s="15"/>
       <c r="C105" s="16">
@@ -13419,7 +13422,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B106" s="15"/>
       <c r="C106" s="16">
@@ -13473,7 +13476,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B107" s="15"/>
       <c r="C107" s="16">
@@ -13537,7 +13540,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B108" s="15"/>
       <c r="C108" s="16">
@@ -13601,7 +13604,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -13659,7 +13662,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B110" s="15"/>
       <c r="C110" s="17">
@@ -13697,7 +13700,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B111" s="15"/>
       <c r="C111" s="17">
@@ -13735,7 +13738,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B112" s="15"/>
       <c r="C112" s="16">
@@ -13773,7 +13776,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -13807,7 +13810,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -13837,7 +13840,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B115" s="16">
         <v>307.43</v>
@@ -13911,7 +13914,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B116" s="16">
         <v>307.43</v>
@@ -13985,7 +13988,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B117" s="15">
         <v>0.0</v>
@@ -14059,7 +14062,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B118" s="17">
         <v>1.0</v>
@@ -14133,7 +14136,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="16">
         <v>225.0</v>
@@ -14205,7 +14208,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -14237,7 +14240,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B121" s="15">
         <v>32000.0</v>
@@ -15200,7 +15203,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15599,73 +15602,73 @@
         <v>45</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15744,7 +15747,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15846,7 +15849,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -15884,7 +15887,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="16">
@@ -15936,7 +15939,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B22" s="16">
         <v>3290.82</v>
@@ -16074,7 +16077,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B24" s="17">
         <v>7.41</v>
@@ -16116,7 +16119,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" s="17">
         <v>23.3</v>
@@ -16182,7 +16185,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B26" s="22">
         <v>-1114.24</v>
@@ -16248,7 +16251,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B27" s="18">
         <v>-45.54</v>
@@ -16378,7 +16381,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -16428,7 +16431,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -16486,7 +16489,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B31" s="17">
         <v>10.59</v>
@@ -16552,7 +16555,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B32" s="16">
         <v>229.84</v>
@@ -16618,7 +16621,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -16650,7 +16653,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -16682,7 +16685,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" s="20">
         <v>2310.03</v>
@@ -16756,7 +16759,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="18">
@@ -16794,7 +16797,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -16842,7 +16845,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -16890,7 +16893,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -16922,7 +16925,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B40" s="22">
         <v>-2758.06</v>
@@ -16996,7 +16999,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B41" s="22">
         <v>-2899.99</v>
@@ -17048,7 +17051,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B42" s="16">
         <v>165.23</v>
@@ -17118,7 +17121,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B43" s="18">
         <v>-10.59</v>
@@ -17182,7 +17185,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -17224,7 +17227,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -17254,7 +17257,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B46" s="23">
         <v>-5503.41</v>
@@ -17328,7 +17331,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -17368,7 +17371,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B48" s="22">
         <v>-1042.22</v>
@@ -17436,7 +17439,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -17474,7 +17477,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B50" s="28">
         <v>-11497.21</v>
@@ -17530,7 +17533,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B51" s="17">
         <v>12.71</v>
@@ -17640,7 +17643,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -17684,7 +17687,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -17716,7 +17719,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -17746,7 +17749,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -17778,7 +17781,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -17816,7 +17819,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -17850,7 +17853,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -17882,7 +17885,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -17912,7 +17915,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -17942,7 +17945,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B62" s="20">
         <v>3035.56</v>
@@ -18016,7 +18019,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B63" s="22">
         <v>-157.82</v>
@@ -18046,7 +18049,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B64" s="16">
         <v>450.51</v>
@@ -18116,7 +18119,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B65" s="15">
         <v>0.0</v>
@@ -18148,7 +18151,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B66" s="16">
         <v>287.58</v>
@@ -18218,7 +18221,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B67" s="23">
         <v>-157.82</v>
@@ -18292,7 +18295,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -19276,7 +19279,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19801,7 +19804,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19899,7 +19902,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -19926,7 +19929,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B21" s="32">
         <v>63777.23</v>
@@ -19991,7 +19994,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B22" s="32">
         <v>56546.2</v>
@@ -20040,7 +20043,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -20067,7 +20070,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B24" s="32">
         <v>33123.53</v>
@@ -20132,7 +20135,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="31" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B25" s="32">
         <v>29896.52</v>
@@ -20189,7 +20192,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="29" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -20216,7 +20219,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B27" s="33">
         <v>107.74</v>
@@ -20281,7 +20284,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="31" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B28" s="34">
         <v>97.25</v>
@@ -20338,7 +20341,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -20365,7 +20368,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B30" s="35">
         <v>-2.46</v>
@@ -20430,7 +20433,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B31" s="35">
         <v>-1.77</v>
@@ -20479,7 +20482,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
@@ -20506,7 +20509,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B33" s="36">
         <v>2.1</v>
@@ -20571,7 +20574,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B34" s="36">
         <v>2.09</v>
@@ -20620,7 +20623,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B35" s="36">
         <v>3.01</v>
@@ -20685,7 +20688,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B36" s="36">
         <v>2.99</v>
@@ -20734,7 +20737,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="29" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -20761,7 +20764,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" s="34">
         <v>1.39</v>
@@ -20826,7 +20829,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B39" s="34">
         <v>1.32</v>
@@ -20875,7 +20878,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
@@ -20902,7 +20905,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="31" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B41" s="34">
         <v>1.39</v>
@@ -20967,7 +20970,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="31" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42" s="34">
         <v>1.32</v>
@@ -21016,7 +21019,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="29" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
@@ -21043,7 +21046,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="31" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B44" s="34">
         <v>7.72</v>
@@ -21108,7 +21111,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B45" s="34">
         <v>8.3</v>
@@ -21157,7 +21160,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
@@ -21184,7 +21187,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="31" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B47" s="32"/>
       <c r="C47" s="32"/>
@@ -21215,7 +21218,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B48" s="30"/>
       <c r="C48" s="30"/>
@@ -21242,7 +21245,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="31" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B49" s="34">
         <v>18.8</v>
@@ -21303,7 +21306,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="31" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B50" s="34">
         <v>15.15</v>
@@ -21352,7 +21355,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="29" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
@@ -21379,7 +21382,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="31" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B52" s="34">
         <v>18.89</v>
@@ -21440,7 +21443,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B53" s="34">
         <v>15.24</v>
@@ -21489,7 +21492,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
@@ -21516,7 +21519,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B55" s="34">
         <v>25.63</v>
@@ -21581,7 +21584,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B56" s="34">
         <v>1.32</v>
@@ -21630,7 +21633,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="29" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
@@ -21657,7 +21660,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B58" s="32">
         <v>0.0</v>
@@ -21716,7 +21719,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B59" s="37">
         <v>-1.49</v>
@@ -21761,7 +21764,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B60" s="30"/>
       <c r="C60" s="30"/>
@@ -21788,7 +21791,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B61" s="34">
         <v>14.86</v>
@@ -21853,7 +21856,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="31" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B62" s="34">
         <v>15.69</v>
@@ -21902,7 +21905,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B63" s="30"/>
       <c r="C63" s="30"/>
@@ -21929,7 +21932,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="31" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B64" s="34">
         <v>21.32</v>
@@ -21994,7 +21997,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B65" s="34">
         <v>22.65</v>
@@ -22043,7 +22046,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B66" s="30"/>
       <c r="C66" s="30"/>
@@ -22070,7 +22073,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="31" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B67" s="34">
         <v>38.36</v>
@@ -22135,7 +22138,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="31" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B68" s="34">
         <v>30.52</v>
@@ -22184,7 +22187,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="29" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B69" s="30"/>
       <c r="C69" s="30"/>
@@ -22211,7 +22214,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="31" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B70" s="32"/>
       <c r="C70" s="32"/>
